--- a/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldAlertTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldAlertTemplate.xlsx
@@ -26,8 +26,64 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+预警寿命（数量）和预警寿命（%）至少填一项
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+预警寿命（数量）和预警寿命（%）至少填一项
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <r>
       <rPr>
@@ -70,6 +126,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -132,6 +194,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -147,6 +215,9 @@
     <t>预警寿命（数量）</t>
   </si>
   <si>
+    <t>预警寿命（%）</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
 </sst>
@@ -160,7 +231,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,6 +399,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1104,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.625" customWidth="1"/>
@@ -1114,12 +1196,12 @@
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="17.875" customWidth="1"/>
     <col min="7" max="7" width="20.125" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="18.125" customWidth="1"/>
+    <col min="8" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1144,7 +1226,10 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1159,5 +1244,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldAlertTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldAlertTemplate.xlsx
@@ -73,7 +73,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-预警寿命（数量）和预警寿命（%）至少填一项
+预警数量和预警比例（%）至少填一项
 </t>
         </r>
       </text>
@@ -212,10 +212,20 @@
     </r>
   </si>
   <si>
-    <t>预警寿命（数量）</t>
+    <t>预警数量</t>
   </si>
   <si>
-    <t>预警寿命（%）</t>
+    <r>
+      <t>预警比例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(%)</t>
+    </r>
   </si>
   <si>
     <t>备注</t>
@@ -231,7 +241,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,6 +409,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldAlertTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldAlertTemplate.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <r>
       <rPr>
@@ -216,6 +216,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>预警比例</t>
     </r>
     <r>
@@ -225,6 +230,43 @@
         <charset val="134"/>
       </rPr>
       <t>(%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>通知类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多个请用英文逗号隔开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
     </r>
   </si>
   <si>
@@ -241,7 +283,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,6 +300,12 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Courier New"/>
       <charset val="134"/>
     </font>
     <font>
@@ -747,137 +795,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -888,6 +936,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1201,7 +1252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="25.625" customWidth="1"/>
@@ -1211,12 +1262,14 @@
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="17.875" customWidth="1"/>
     <col min="7" max="7" width="20.125" customWidth="1"/>
-    <col min="8" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="18.125" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="35.25" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1241,10 +1294,13 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3"/>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
